--- a/R02NEW.xlsx
+++ b/R02NEW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\project\claude\4BFR2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA24C34-2D03-45E1-B669-C00005ED462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFAF3EE-5C95-4A9B-825D-CB12EFE1738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1474" yWindow="1474" windowWidth="16457" windowHeight="9455" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1509" yWindow="1509" windowWidth="20040" windowHeight="10277" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21437,7 +21437,7 @@
         <v>957</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>24</v>
